--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488001_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488001_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4044</v>
+        <v>7.6298</v>
       </c>
       <c r="E2" t="n">
-        <v>8.814</v>
+        <v>6.5729</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5904</v>
+        <v>1.0569</v>
       </c>
       <c r="G2" t="n">
         <v>5.9615</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2973</v>
+        <v>2.5227</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3884</v>
+        <v>1.1473</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9089</v>
+        <v>1.3754</v>
       </c>
       <c r="V2" t="n">
         <v>0.5331</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0276</v>
+        <v>4.4221</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3076</v>
+        <v>0.8287</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.28</v>
+        <v>3.5934</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5431</v>
+        <v>0.2109</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1408</v>
+        <v>-1.4154</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4023</v>
+        <v>1.6263</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1196</v>
+        <v>0.6319</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8702</v>
+        <v>0.6526</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2494</v>
+        <v>-0.0207</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5765</v>
+        <v>-0.421</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7294</v>
+        <v>-2.068</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1529</v>
+        <v>1.647</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1893</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6321</v>
+        <v>0.4074</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9215</v>
+        <v>-0.0191</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2894</v>
+        <v>0.4265</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.337</v>
+        <v>2.218</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6036</v>
+        <v>1.0109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2672</v>
+        <v>3.7781</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4925</v>
+        <v>4.002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7747000000000001</v>
+        <v>-0.2239</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5786</v>
+        <v>2.5431</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3987</v>
+        <v>1.1408</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9773</v>
+        <v>1.4023</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6691</v>
+        <v>3.1196</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9371</v>
+        <v>1.8702</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7321</v>
+        <v>1.2494</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0905</v>
+        <v>-0.5765</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3357</v>
+        <v>-0.7294</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2452</v>
+        <v>0.1529</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4815</v>
+        <v>0.3827</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1944</v>
+        <v>0.6159</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6758999999999999</v>
+        <v>-0.2332</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9718</v>
+        <v>3.3482</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0881</v>
+        <v>2.7981</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0599</v>
+        <v>0.5501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2109</v>
+        <v>3.5786</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4154</v>
+        <v>-0.3987</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6263</v>
+        <v>3.9773</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6319</v>
+        <v>4.6691</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6526</v>
+        <v>1.9371</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0207</v>
+        <v>2.7321</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.421</v>
+        <v>-1.0905</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.068</v>
+        <v>-2.3357</v>
       </c>
       <c r="O5" t="n">
-        <v>1.647</v>
+        <v>1.2452</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5858</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5769</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0429</v>
+        <v>0.5624</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0.1112</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.107</v>
+        <v>0.4513</v>
       </c>
       <c r="V5" t="n">
-        <v>2.218</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.238</v>
+        <v>2.4979</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7346</v>
+        <v>1.9384</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5033</v>
+        <v>0.5595</v>
       </c>
       <c r="G6" t="n">
         <v>2.5359</v>
@@ -922,13 +922,13 @@
         <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2563</v>
+        <v>0.0036</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6864</v>
+        <v>-0.4826</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4301</v>
+        <v>0.4863</v>
       </c>
       <c r="V6" t="n">
         <v>1.5441</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9918</v>
+        <v>1.6102</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1839</v>
+        <v>0.6311</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1757</v>
+        <v>0.9791</v>
       </c>
       <c r="G7" t="n">
         <v>4.3759</v>
@@ -1000,13 +1000,13 @@
         <v>2.5769</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2303</v>
+        <v>0.3881</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0608</v>
+        <v>-0.2458</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8304</v>
+        <v>0.6339</v>
       </c>
       <c r="V7" t="n">
         <v>1.2071</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0341</v>
+        <v>0.0902</v>
       </c>
       <c r="E8" t="n">
         <v>1.3428</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3087</v>
+        <v>-1.2525</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0857</v>
@@ -1078,13 +1078,13 @@
         <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2856</v>
+        <v>-0.2294</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V8" t="n">
         <v>1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6459</v>
+        <v>-1.5721</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2487</v>
+        <v>-1.1469</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3972</v>
+        <v>-0.4253</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0016</v>
@@ -1234,13 +1234,13 @@
         <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0408</v>
+        <v>0.033</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3336</v>
+        <v>0.3055</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9408</v>
+        <v>-3.025</v>
       </c>
       <c r="E11" t="n">
         <v>-2.4416</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4992</v>
+        <v>-0.5834</v>
       </c>
       <c r="G11" t="n">
         <v>0.1108</v>
@@ -1312,13 +1312,13 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2764</v>
+        <v>-0.3607</v>
       </c>
       <c r="T11" t="n">
         <v>-0.4368</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1603</v>
+        <v>0.0761</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VILLEGAS ACIEN</t>
+          <t>C. RAMON PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3389</v>
+        <v>-3.2539</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.454</v>
+        <v>-2.2562</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.885</v>
+        <v>-0.9976</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.343</v>
+        <v>-3.1571</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6639</v>
+        <v>-2.4951</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6791</v>
+        <v>-0.662</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3381</v>
+        <v>-1.7112</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.659</v>
+        <v>-1.1565</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6791</v>
+        <v>-0.5547</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.005</v>
+        <v>-1.446</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.005</v>
+        <v>-1.3386</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0.1073</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9911</v>
+        <v>1.5858</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0048</v>
+        <v>-0.4754</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1248</v>
+        <v>-0.545</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.0696</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. RAMON PEREZ</t>
+          <t>A. VILLEGAS ACIEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9069</v>
+        <v>-3.4232</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.46</v>
+        <v>-2.454</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4469</v>
+        <v>-0.9692</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1571</v>
+        <v>-2.343</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4951</v>
+        <v>-1.6639</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.662</v>
+        <v>-0.6791</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7112</v>
+        <v>-1.3381</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1565</v>
+        <v>-0.659</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5547</v>
+        <v>-0.6791</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.446</v>
+        <v>-1.005</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3386</v>
+        <v>-1.005</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1073</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5858</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1284</v>
+        <v>-0.089</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7488</v>
+        <v>-0.1248</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3796</v>
+        <v>0.0358</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.0953</v>
+        <v>11.0952</v>
       </c>
       <c r="E14" t="n">
-        <v>9.815200000000001</v>
+        <v>9.815299999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>1.279899999999999</v>
+        <v>1.279999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>10.4616</v>
@@ -1519,7 +1519,7 @@
         <v>12.7893</v>
       </c>
       <c r="J14" t="n">
-        <v>23.5787</v>
+        <v>23.57869999999999</v>
       </c>
       <c r="K14" t="n">
         <v>15.7142</v>
@@ -1537,7 +1537,7 @@
         <v>4.9249</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.9379</v>
+        <v>-6.937900000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-19.8221</v>
@@ -1546,13 +1546,13 @@
         <v>12.8844</v>
       </c>
       <c r="S14" t="n">
-        <v>3.009600000000001</v>
+        <v>3.0096</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4397</v>
+        <v>-0.4393999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>3.449</v>
+        <v>3.4492</v>
       </c>
       <c r="V14" t="n">
         <v>4.5617</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6147</v>
+        <v>5.7051</v>
       </c>
       <c r="E15" t="n">
-        <v>8.0555</v>
+        <v>7.3424</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4408</v>
+        <v>-1.6373</v>
       </c>
       <c r="G15" t="n">
         <v>5.323</v>
@@ -1624,13 +1624,13 @@
         <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9042</v>
+        <v>-0.0054</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6022999999999999</v>
+        <v>-0.1108</v>
       </c>
       <c r="U15" t="n">
-        <v>0.302</v>
+        <v>0.1054</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6036</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.725</v>
+        <v>3.7322</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2657</v>
+        <v>2.4695</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4593</v>
+        <v>1.2627</v>
       </c>
       <c r="G16" t="n">
         <v>1.6213</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2155</v>
+        <v>-0.2083</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6129</v>
+        <v>-0.4092</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3974</v>
+        <v>0.2009</v>
       </c>
       <c r="V16" t="n">
         <v>0.337</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3869</v>
+        <v>1.1061</v>
       </c>
       <c r="E17" t="n">
         <v>0.607</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7799</v>
+        <v>0.4991</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7974</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2717</v>
+        <v>-0.5524</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2458</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0259</v>
+        <v>-0.3066</v>
       </c>
       <c r="V17" t="n">
         <v>0.8701</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>J. LUCAS SERRANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0578</v>
+        <v>-0.2581</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9229</v>
+        <v>0.5962</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9807</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9534</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3775</v>
+        <v>0.3514</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.3309</v>
+        <v>-0.266</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9842</v>
+        <v>0.6192</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8608</v>
+        <v>0.6192</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8767</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9375</v>
+        <v>-0.5337</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4833</v>
+        <v>-0.2677</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4542</v>
+        <v>-0.266</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4814</v>
+        <v>0.0707</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1103</v>
+        <v>-0.0229</v>
       </c>
       <c r="U19" t="n">
-        <v>0.371</v>
+        <v>0.0936</v>
       </c>
       <c r="V19" t="n">
-        <v>1.8107</v>
+        <v>-1.2071</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LUCAS SERRANO</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4161</v>
+        <v>-0.6409</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4944</v>
+        <v>1.3117</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9105</v>
+        <v>-1.9526</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08550000000000001</v>
+        <v>-1.9534</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3514</v>
+        <v>1.3775</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.266</v>
+        <v>-3.3309</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6192</v>
+        <v>1.9842</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6192</v>
+        <v>3.8608</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.8767</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5337</v>
+        <v>-3.9375</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2677</v>
+        <v>-2.4833</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.266</v>
+        <v>-1.4542</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7929</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1018</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1248</v>
+        <v>-0.5009</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0374</v>
+        <v>0.3991</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2071</v>
+        <v>1.8107</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8232</v>
+        <v>-0.6542</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8663</v>
+        <v>-1.8094</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0431</v>
+        <v>1.1552</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6734</v>
+        <v>1.1681</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5433</v>
+        <v>1.6196</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1301</v>
+        <v>-0.4515</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6791</v>
+        <v>2.018</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6791</v>
+        <v>2.6167</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.5988</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0057</v>
+        <v>-0.8499</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1358</v>
+        <v>-0.9971</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1301</v>
+        <v>0.1472</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1498</v>
+        <v>-0.1661</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1872</v>
+        <v>0.2075</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0374</v>
+        <v>-0.3736</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8298</v>
+        <v>-0.767</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0131</v>
+        <v>-0.8663</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1833</v>
+        <v>0.0993</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1681</v>
+        <v>-0.6734</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6196</v>
+        <v>-0.5433</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4515</v>
+        <v>-0.1301</v>
       </c>
       <c r="J22" t="n">
-        <v>2.018</v>
+        <v>-0.6791</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6167</v>
+        <v>-0.6791</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5988</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8499</v>
+        <v>0.0057</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9971</v>
+        <v>0.1358</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1472</v>
+        <v>-0.1301</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3417</v>
+        <v>-0.0936</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0038</v>
+        <v>-0.1872</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3455</v>
+        <v>0.0936</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SIMON DIAZ</t>
+          <t>A. LOPEZ MENACHO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.024</v>
+        <v>-1.2922</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4794</v>
+        <v>-2.094</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5034</v>
+        <v>0.8018</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2392</v>
+        <v>0.0063</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8686</v>
+        <v>-1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6294</v>
+        <v>1.2263</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4845</v>
+        <v>0.0644</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4041</v>
+        <v>-0.6186</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0804</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7237</v>
+        <v>-0.0581</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2727</v>
+        <v>-0.6014</v>
       </c>
       <c r="O23" t="n">
-        <v>0.549</v>
+        <v>0.5433</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9822</v>
+        <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8542999999999999</v>
+        <v>-0.3074</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9949</v>
+        <v>-0.1762</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1406</v>
+        <v>-0.1313</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.6213</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.6213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. LOPEZ MENACHO</t>
+          <t>A. SIMON DIAZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3764</v>
+        <v>-1.3368</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.094</v>
+        <v>0.97</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7175</v>
+        <v>-2.3068</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0063</v>
+        <v>-0.2392</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.22</v>
+        <v>-0.8686</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2263</v>
+        <v>0.6294</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0644</v>
+        <v>0.4845</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6186</v>
+        <v>0.4041</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.0804</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0581</v>
+        <v>-0.7237</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6014</v>
+        <v>-1.2727</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5433</v>
+        <v>0.549</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3917</v>
+        <v>0.5415</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1762</v>
+        <v>0.4856</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2155</v>
+        <v>0.0559</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-3.6213</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-3.6213</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3806</v>
+        <v>-4.5833</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3519</v>
+        <v>-2.6388</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0288</v>
+        <v>-1.9445</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5412</v>
@@ -2404,13 +2404,13 @@
         <v>2.9733</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8306</v>
+        <v>-1.0333</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5599</v>
+        <v>-0.8468</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2707</v>
+        <v>-0.1864</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.107</v>
+        <v>-5.1692</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7457</v>
+        <v>-3.0326</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3613</v>
+        <v>-2.1366</v>
       </c>
       <c r="G26" t="n">
         <v>-4.9133</v>
@@ -2482,13 +2482,13 @@
         <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9866</v>
+        <v>-1.0489</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4975</v>
+        <v>-0.7844</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.489</v>
+        <v>-0.2644</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.4122</v>
+        <v>-7.5421</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.6392</v>
+        <v>-4.741</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.773</v>
+        <v>-2.8011</v>
       </c>
       <c r="G27" t="n">
         <v>-6.1532</v>
@@ -2560,13 +2560,13 @@
         <v>1.784</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0254</v>
+        <v>-0.1045</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.756</v>
+        <v>-0.8579</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7814</v>
+        <v>0.7533</v>
       </c>
       <c r="V27" t="n">
         <v>-2.0772</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-11.0952</v>
+        <v>-11.0951</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.279999999999999</v>
+        <v>-1.279999999999997</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.8154</v>
+        <v>-9.815099999999999</v>
       </c>
       <c r="G28" t="n">
         <v>-10.4616</v>
@@ -2629,7 +2629,7 @@
         <v>-7.8646</v>
       </c>
       <c r="P28" t="n">
-        <v>6.9378</v>
+        <v>6.937800000000001</v>
       </c>
       <c r="Q28" t="n">
         <v>-12.8844</v>
@@ -2638,13 +2638,13 @@
         <v>19.8222</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.0097</v>
+        <v>-3.0095</v>
       </c>
       <c r="T28" t="n">
         <v>-3.449</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4394</v>
+        <v>0.4395</v>
       </c>
       <c r="V28" t="n">
         <v>-4.5618</v>
